--- a/sheets/조재수대금교본/검수/정선 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/정선 아리랑.xlsx
@@ -3890,8 +3890,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-Z</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -3910,7 +3909,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㄷ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -3924,7 +3923,7 @@
       <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-汰⌝</t>
+汰</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -3934,28 +3933,20 @@
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D4" s="21"/>
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="G4" s="23"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H4" s="21"/>
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
@@ -3965,16 +3956,11 @@
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZZ
-–</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N4" s="21"/>
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
@@ -3992,44 +3978,30 @@
         </is>
       </c>
       <c r="C5" s="24"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰㳞
+          <t xml:space="preserve">汰㳞
 △</t>
         </is>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-汰㳞
-‹</t>
+          <t xml:space="preserve">㳞
+汰㳞</t>
         </is>
       </c>
       <c r="K5" s="24"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-汰㳞
-‹</t>
+          <t xml:space="preserve">㳞
+汰㳞</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -4040,7 +4012,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㄷ
+          <t xml:space="preserve">淋
 –</t>
         </is>
       </c>
@@ -4054,21 +4026,20 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㄷ
+          <t xml:space="preserve">淋
 –</t>
         </is>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-Z</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㄷ
+          <t xml:space="preserve">淋
 –</t>
         </is>
       </c>
@@ -4082,7 +4053,7 @@
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞淋∧
+          <t xml:space="preserve">㳞淋
 –</t>
         </is>
       </c>
@@ -4090,7 +4061,7 @@
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-汰⌝</t>
+汰</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -4099,50 +4070,50 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-–ﾉ</t>
+          <t xml:space="preserve">㳞
+–</t>
         </is>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–И</t>
+–</t>
         </is>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-–ﾉ</t>
+          <t xml:space="preserve">㳞
+–</t>
         </is>
       </c>
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-–ﾉ</t>
+          <t xml:space="preserve">㳞
+–</t>
         </is>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-–ﾉ</t>
+          <t xml:space="preserve">㳞
+–</t>
         </is>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -4157,65 +4128,54 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
     <row r="9" ht="96.05" customHeight="true">
@@ -4253,7 +4213,7 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰Z
+          <t xml:space="preserve">汰
 –</t>
         </is>
       </c>
@@ -4277,56 +4237,55 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–И</t>
+–</t>
         </is>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
+          <t xml:space="preserve">汰
 㳞</t>
         </is>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zㄱ
-㳞ʒ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
@@ -4335,7 +4294,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
+          <t xml:space="preserve">汰
 南</t>
         </is>
       </c>
@@ -4348,42 +4307,41 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
+          <t xml:space="preserve">汰
 南</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞∧
-ﾉ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
+          <t xml:space="preserve">汰
 南</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
+          <t xml:space="preserve">汰潢
 南汰</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
+          <t xml:space="preserve">汰
 南</t>
         </is>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
+          <t xml:space="preserve">汰潢
 南汰</t>
         </is>
       </c>
@@ -4433,11 +4391,7 @@
         </is>
       </c>
       <c r="O12" s="22"/>
-      <c r="P12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P12" s="21"/>
       <c r="Q12" s="22"/>
     </row>
     <row r="13" ht="96.05" customHeight="true">
@@ -4454,14 +4408,14 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰⌝</t>
+汰</t>
         </is>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -4470,7 +4424,7 @@
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="M13" s="23"/>
@@ -4479,7 +4433,7 @@
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="Q13" s="23"/>
@@ -4495,24 +4449,21 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -4525,9 +4476,8 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="M14" s="24"/>
@@ -4535,9 +4485,8 @@
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南
-‹</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="Q14" s="24"/>

--- a/sheets/조재수대금교본/검수/정선 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/정선 아리랑.xlsx
@@ -3890,7 +3890,8 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰
+Z</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -3909,7 +3910,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㄷ</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -3923,7 +3924,7 @@
       <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-汰</t>
+汰⌝</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -3933,20 +3934,28 @@
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="G4" s="23"/>
-      <c r="H4" s="21"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
@@ -3956,11 +3965,16 @@
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">ZZ
+–</t>
         </is>
       </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
@@ -3978,11 +3992,15 @@
         </is>
       </c>
       <c r="C5" s="24"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞
+          <t xml:space="preserve">∽汰㳞
 △</t>
         </is>
       </c>
@@ -3991,16 +4009,20 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ʒ
 汰㳞</t>
         </is>
       </c>
       <c r="K5" s="24"/>
-      <c r="L5" s="21"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ʒ
 汰㳞</t>
         </is>
       </c>
@@ -4012,7 +4034,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
+          <t xml:space="preserve">淋ㄷ
 –</t>
         </is>
       </c>
@@ -4026,20 +4048,21 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
+          <t xml:space="preserve">淋ㄷ
 –</t>
         </is>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰
+Z</t>
         </is>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
+          <t xml:space="preserve">淋ㄷ
 –</t>
         </is>
       </c>
@@ -4053,7 +4076,7 @@
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞淋
+          <t xml:space="preserve">㳞淋∧
 –</t>
         </is>
       </c>
@@ -4061,7 +4084,7 @@
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-汰</t>
+汰⌝</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -4070,50 +4093,50 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-–</t>
+          <t xml:space="preserve">㳞ʒ
+–ﾉ</t>
         </is>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–</t>
+–И</t>
         </is>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-–</t>
+          <t xml:space="preserve">㳞ʒ
+–ﾉ</t>
         </is>
       </c>
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-–</t>
+          <t xml:space="preserve">㳞ʒ
+–ﾉ</t>
         </is>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-–</t>
+          <t xml:space="preserve">㳞ʒ
+–ﾉ</t>
         </is>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -4128,7 +4151,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
@@ -4142,35 +4165,35 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
@@ -4213,7 +4236,7 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰Z
 –</t>
         </is>
       </c>
@@ -4237,55 +4260,56 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–</t>
+–И</t>
         </is>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∧
 㳞</t>
         </is>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">Zㄱ
+㳞ʒ</t>
         </is>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
@@ -4294,7 +4318,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
@@ -4307,41 +4331,42 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞∧
+ﾉ</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">∽汰潢
 南汰</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">∽汰潢
 南汰</t>
         </is>
       </c>
@@ -4391,7 +4416,11 @@
         </is>
       </c>
       <c r="O12" s="22"/>
-      <c r="P12" s="21"/>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q12" s="22"/>
     </row>
     <row r="13" ht="96.05" customHeight="true">
@@ -4408,14 +4437,14 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+汰⌝</t>
         </is>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -4424,7 +4453,7 @@
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="M13" s="23"/>
@@ -4433,7 +4462,7 @@
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="Q13" s="23"/>
@@ -4449,7 +4478,7 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
@@ -4462,7 +4491,7 @@
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
@@ -4476,7 +4505,7 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
@@ -4485,7 +4514,7 @@
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/정선 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/정선 아리랑.xlsx
@@ -3829,28 +3829,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="74.07" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="110.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="110.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="110.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="110.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="110.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="110.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="110.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="110.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="110.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="110.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="110.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="110.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4526,6 +4526,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="54"/>
 </worksheet>
 </file>